--- a/artfynd/A 15852-2026 artfynd.xlsx
+++ b/artfynd/A 15852-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136189328</v>
       </c>
       <c r="B2" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 15852-2026 artfynd.xlsx
+++ b/artfynd/A 15852-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136189328</v>
       </c>
       <c r="B2" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 15852-2026 artfynd.xlsx
+++ b/artfynd/A 15852-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136189328</v>
       </c>
       <c r="B2" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 15852-2026 artfynd.xlsx
+++ b/artfynd/A 15852-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136189328</v>
       </c>
       <c r="B2" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 15852-2026 artfynd.xlsx
+++ b/artfynd/A 15852-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136189328</v>
       </c>
       <c r="B2" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 15852-2026 artfynd.xlsx
+++ b/artfynd/A 15852-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136189328</v>
       </c>
       <c r="B2" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 15852-2026 artfynd.xlsx
+++ b/artfynd/A 15852-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136189328</v>
       </c>
       <c r="B2" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 15852-2026 artfynd.xlsx
+++ b/artfynd/A 15852-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136189328</v>
       </c>
       <c r="B2" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 15852-2026 artfynd.xlsx
+++ b/artfynd/A 15852-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136189328</v>
       </c>
       <c r="B2" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
